--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.25" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0025.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0025.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.25" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -603,18 +603,18 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dress.â€” 2. The names of the parties.â€” 3. A statement</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing. This Bill formerly consisted of nine parts,â€”1. The ad-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]3. It il</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]3. It il</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: isolated marker/symbol line :: g</t>
@@ -628,7 +628,7 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: must containâ€”-...</t>
+          <t>L79: punctuation artifact: repeated periods :: must contain—-...</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,16 +670,8 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” 5. Particular charges in answer to what the Defendant</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dress.â€”2. The names of the parties.â€”3. A statement</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -729,16 +721,8 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pretends to be his case.â€” 6. An averment that the</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the facts.â€”4. A general charge against the Defendant.</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -766,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -780,16 +764,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: conscience.â€” 7. The interrogatories, Defendant</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”5. Particular charges in answer to what the Defendant</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -827,16 +803,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prayer for relief.â€” And 9. The prayer for process or</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pretends to be his case.â€”6. An averment that the</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -874,16 +842,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: writ of subpo Ã¦ to compel the defendant appear and</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: conscience.â€”7. The interrogatories, which the Defendant</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -921,16 +881,8 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: must contain â€”</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: &gt;was bound to answer substantially and literally.â€”8. The</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
@@ -968,16 +920,8 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dress.â€” 2. The names of the parties.â€” 3. A statement</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prayer for relief.â€”And 9. The prayer for process or</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1001,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1015,16 +959,8 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” 5. Particular charges in answer to what the Defendant</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: scribed by the following order :â€”</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1053,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1062,16 +998,8 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pretends to be his case.â€” 6. An averment that the</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: must containâ€”-...</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1109,11 +1037,7 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: conscience.â€” 7. The interrogatories, Defendant</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
@@ -1152,11 +1076,7 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prayer for relief.â€” And 9. The prayer for process or</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
@@ -1195,11 +1115,7 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: writ of subpo Ã¦ to compel the defendant appear and</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
@@ -1238,11 +1154,7 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: must contain â€”</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
